--- a/generated/spreadsheet/verbose/approval-of-details-reserved-by-condition-approval-condition-verbose.xlsx
+++ b/generated/spreadsheet/verbose/approval-of-details-reserved-by-condition-approval-condition-verbose.xlsx
@@ -1024,7 +1024,7 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Planning requirement references identifying the information this document provides. A document may address more than one requirement. These references identify its coverage; they do not establish that the requirements have been satisfied.</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Discharge condition</t>
+          <t>Discharge of conditions</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>How any conditions imposed as part of being given planning permission will be met</t>
+          <t>Information submitted to demonstrate how the requirements of one or more planning conditions will be met</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>description-list</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Description list</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3452,7 +3452,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Description or list of materials/details that are being submitted for approval</t>
+          <t>A full description or list of the materials or other details submitted for approval</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
